--- a/data/trans_orig/P32A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1816</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6909</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273722</t>
+          <t>273723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>184601</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186417</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460221</t>
+          <t>459892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491314</t>
+          <t>490935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499942</t>
+          <t>499929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210656</t>
+          <t>210640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705070</t>
+          <t>705270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715963</t>
+          <t>716106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390528</t>
+          <t>391214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399876</t>
+          <t>399945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217336</t>
+          <t>218357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611559</t>
+          <t>613389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623239</t>
+          <t>623268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,62 +1797,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7189</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307141</t>
+          <t>305097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>452440</t>
+          <t>451508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168869</t>
+          <t>167184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178413</t>
+          <t>177632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73510</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242656</t>
+          <t>242504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253716</t>
+          <t>253559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157340</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,62 +2826,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2083</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4996</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68027</t>
+          <t>68073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84664</t>
+          <t>83990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1849926</t>
+          <t>1850945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1868000</t>
+          <t>1868939</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>885575</t>
+          <t>885511</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>892575</t>
+          <t>892579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2740243</t>
+          <t>2739237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2759218</t>
+          <t>2759126</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262890</t>
+          <t>262809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274947</t>
+          <t>274826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177313</t>
+          <t>176372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444198</t>
+          <t>444225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456716</t>
+          <t>456684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>21975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446286</t>
+          <t>445822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>460412</t>
+          <t>459908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206662</t>
+          <t>205985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655753</t>
+          <t>655071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>670845</t>
+          <t>670939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402151</t>
+          <t>404959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419337</t>
+          <t>419967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238632</t>
+          <t>237567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646579</t>
+          <t>646072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662196</t>
+          <t>662181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>372044</t>
+          <t>371926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387001</t>
+          <t>387073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207350</t>
+          <t>207967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>583993</t>
+          <t>582361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>599746</t>
+          <t>599848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220755</t>
+          <t>220770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100100</t>
+          <t>99366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111187</t>
+          <t>111169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329095</t>
+          <t>328980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>342779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145350</t>
+          <t>145044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202020</t>
+          <t>201754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209072</t>
+          <t>209066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>12142</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>12360</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>97758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79962</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1965967</t>
+          <t>1965986</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1997576</t>
+          <t>1997200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1026850</t>
+          <t>1026322</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1040431</t>
+          <t>1040374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2999865</t>
+          <t>3001573</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3035506</t>
+          <t>3034781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245120</t>
+          <t>244861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164143</t>
+          <t>163756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171557</t>
+          <t>171549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413829</t>
+          <t>413311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425390</t>
+          <t>425193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18985</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346547</t>
+          <t>346616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359913</t>
+          <t>360239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218009</t>
+          <t>218079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568684</t>
+          <t>569270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583913</t>
+          <t>583832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416458</t>
+          <t>415815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428040</t>
+          <t>428296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242757</t>
+          <t>243632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662728</t>
+          <t>662658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675880</t>
+          <t>675839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>372553</t>
+          <t>370989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>385341</t>
+          <t>385142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259488</t>
+          <t>258532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636782</t>
+          <t>636288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>650029</t>
+          <t>650226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>273965</t>
+          <t>274374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284515</t>
+          <t>284549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118223</t>
+          <t>117761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128413</t>
+          <t>128418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396751</t>
+          <t>397406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411776</t>
+          <t>411709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169801</t>
+          <t>169676</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176585</t>
+          <t>176583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233980</t>
+          <t>234817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242858</t>
+          <t>242816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -8749,97 +8749,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1648</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1194</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5795</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6010</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6975</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93779</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30780</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125026</t>
+          <t>125991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54016</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1947346</t>
+          <t>1946020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1974089</t>
+          <t>1972515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1118979</t>
+          <t>1120346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1136729</t>
+          <t>1136498</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3076132</t>
+          <t>3075669</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3105205</t>
+          <t>3105519</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85713</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98621</t>
+          <t>98736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254829</t>
+          <t>254871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268477</t>
+          <t>268655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222620</t>
+          <t>222050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135171</t>
+          <t>135277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361239</t>
+          <t>361551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369974</t>
+          <t>370016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272754</t>
+          <t>272898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149652</t>
+          <t>149650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>422153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429529</t>
+          <t>429588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325460</t>
+          <t>326269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336856</t>
+          <t>336920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182966</t>
+          <t>183981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188081</t>
+          <t>187931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512116</t>
+          <t>511511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>524107</t>
+          <t>524197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19568</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246062</t>
+          <t>245484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257655</t>
+          <t>257078</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128175</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133636</t>
+          <t>133632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378040</t>
+          <t>377727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389844</t>
+          <t>389825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180245</t>
+          <t>180706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187372</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272424</t>
+          <t>272137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454928</t>
+          <t>454885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467122</t>
+          <t>466873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93839</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>99341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>120414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125658</t>
+          <t>125643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38761</t>
+          <t>39309</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56615</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1534776</t>
+          <t>1534228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1553617</t>
+          <t>1554131</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>993982</t>
+          <t>994306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1012236</t>
+          <t>1012417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2535366</t>
+          <t>2536440</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2562270</t>
+          <t>2563444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273723</t>
+          <t>273958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459892</t>
+          <t>459952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490935</t>
+          <t>491197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499929</t>
+          <t>499942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210640</t>
+          <t>211142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705270</t>
+          <t>706283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716106</t>
+          <t>716159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>391214</t>
+          <t>390726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399945</t>
+          <t>399960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218357</t>
+          <t>217472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613389</t>
+          <t>612646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623268</t>
+          <t>623236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305097</t>
+          <t>306117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451508</t>
+          <t>452383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167184</t>
+          <t>167267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177632</t>
+          <t>178244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242504</t>
+          <t>242262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253559</t>
+          <t>253587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68073</t>
+          <t>68064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1850945</t>
+          <t>1851211</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1868939</t>
+          <t>1868558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>885511</t>
+          <t>885493</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>892579</t>
+          <t>892575</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2739237</t>
+          <t>2738894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2759126</t>
+          <t>2759023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262809</t>
+          <t>262880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274826</t>
+          <t>275001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176372</t>
+          <t>176444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444225</t>
+          <t>444033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456684</t>
+          <t>456700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445822</t>
+          <t>446757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459908</t>
+          <t>460237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>205985</t>
+          <t>206829</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655071</t>
+          <t>656590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>670939</t>
+          <t>670779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404959</t>
+          <t>403225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419967</t>
+          <t>419324</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237567</t>
+          <t>238191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646072</t>
+          <t>646498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662181</t>
+          <t>661791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>19649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371926</t>
+          <t>372765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387073</t>
+          <t>387070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207967</t>
+          <t>207910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582361</t>
+          <t>584525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>599848</t>
+          <t>599775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220770</t>
+          <t>218328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99366</t>
+          <t>100976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111169</t>
+          <t>111182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>328980</t>
+          <t>326825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342779</t>
+          <t>342068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>145689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152539</t>
+          <t>152544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201754</t>
+          <t>202070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209066</t>
+          <t>209048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>74115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97758</t>
+          <t>98801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69394</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45046</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1965986</t>
+          <t>1964811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1997200</t>
+          <t>1996252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1026322</t>
+          <t>1027220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1040374</t>
+          <t>1040624</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3001573</t>
+          <t>2999575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3034781</t>
+          <t>3033590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244861</t>
+          <t>245332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254058</t>
+          <t>254073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163756</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171549</t>
+          <t>171558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413311</t>
+          <t>413386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425193</t>
+          <t>425142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346616</t>
+          <t>346627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360239</t>
+          <t>360448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218079</t>
+          <t>217900</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>569270</t>
+          <t>569510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583832</t>
+          <t>583633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415815</t>
+          <t>415729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428296</t>
+          <t>427692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243632</t>
+          <t>243540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662658</t>
+          <t>663010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675839</t>
+          <t>675860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370989</t>
+          <t>371734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>385142</t>
+          <t>385271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258532</t>
+          <t>258531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636288</t>
+          <t>634870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>650226</t>
+          <t>650005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>274390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284549</t>
+          <t>284512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117761</t>
+          <t>118543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128418</t>
+          <t>128425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397406</t>
+          <t>396679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411709</t>
+          <t>411799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169676</t>
+          <t>169328</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176583</t>
+          <t>176595</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234817</t>
+          <t>234235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242816</t>
+          <t>242905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125991</t>
+          <t>124469</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>53413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>71659</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1946020</t>
+          <t>1947949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1972515</t>
+          <t>1973449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1120346</t>
+          <t>1120552</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1136498</t>
+          <t>1136949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3075669</t>
+          <t>3075015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3105519</t>
+          <t>3106108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94918</t>
+          <t>103152</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86621</t>
+          <t>93091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98736</t>
+          <t>108772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264821</t>
+          <t>269395</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254871</t>
+          <t>256691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268655</t>
+          <t>274914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>228577</t>
+          <t>248228</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222050</t>
+          <t>243039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>138961</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135277</t>
+          <t>145080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>367538</t>
+          <t>397958</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361551</t>
+          <t>392817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>370016</t>
+          <t>400139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>278813</t>
+          <t>308191</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272898</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280992</t>
+          <t>310520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148138</t>
+          <t>167062</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>168689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>426951</t>
+          <t>475252</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>422153</t>
+          <t>468367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429588</t>
+          <t>478811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>332738</t>
+          <t>341468</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326269</t>
+          <t>334102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336920</t>
+          <t>345905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>186766</t>
+          <t>206290</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183981</t>
+          <t>202782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187931</t>
+          <t>207712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>519504</t>
+          <t>547760</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>511511</t>
+          <t>539633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>524197</t>
+          <t>552926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>208402</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>208402</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>208402</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>528403</t>
+          <t>558162</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>528403</t>
+          <t>558162</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>528403</t>
+          <t>558162</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19881</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>253006</t>
+          <t>269658</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245484</t>
+          <t>263210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257078</t>
+          <t>274027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>131842</t>
+          <t>144834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128215</t>
+          <t>140678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133632</t>
+          <t>146789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>384847</t>
+          <t>414491</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377727</t>
+          <t>407298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389825</t>
+          <t>419917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>429</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>184860</t>
+          <t>201786</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180706</t>
+          <t>196953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187204</t>
+          <t>204866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>277533</t>
+          <t>77575</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272137</t>
+          <t>75366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>462392</t>
+          <t>279362</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454885</t>
+          <t>273780</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466873</t>
+          <t>282596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93718</t>
+          <t>103891</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>109173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>26812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>123844</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>133223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125643</t>
+          <t>139292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>42024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>65653</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1545549</t>
+          <t>1642867</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1534228</t>
+          <t>1631279</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1554131</t>
+          <t>1652198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1004348</t>
+          <t>878332</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>994306</t>
+          <t>866783</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1012417</t>
+          <t>886020</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2549897</t>
+          <t>2521200</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2536440</t>
+          <t>2505357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2563444</t>
+          <t>2533032</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
